--- a/docs/项目配置填写表.xlsx
+++ b/docs/项目配置填写表.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +47,21 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B07D12"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="007A560C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="001B5E9A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +90,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FBF3DF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFDE7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,74 +126,52 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,12 +539,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -552,288 +554,414 @@
           <t>游戏术语抽取 — 项目信息填写表</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>🟡 黄色区域请填写  |  灰色为填写提示，不用修改  |  填完后原文件发回即可</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>🟡 只填最后一列（黄色）  |  第三列是燕云项目参考示例，照着写  |  ★ 题最影响准确率，请重点写  |  详见配套《Profile撰写指南.html》</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>零、开工前先备齐这些资料（不用填，自查清单）</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>☐ 源文件</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>游戏文本 .xlsx，至少一列是中文原文。变量占位符（{0}、${name}、&lt;color&gt; 等）自动剥离，不用手动清。可多文件分批（剧情/UI/技能拆开更好管）。</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>☐ 术语表 ★命门</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>已有「中文术语 | 英文翻译」两列的 .xlsx。它是准确率命门：命中词被保护不误删、直接套用已有译文、并作新词近义参考——实测约九成召回靠它。来源：官方词表 / 历史项目 TM / 人物表 / 技能表 / 道具表，能并就并，越全越准。没有？先凑核心人物+核心系统词的小表垫着，跑完把确认的术语回灌，边跑边长。</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>☐ 填表素材</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>世界观设定、人物/技能/道具/地名表、游戏系统结构、试译反馈、客户 brief——用来把下面 12 题填准。</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>填写提示</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>✍ 参考示例（燕云）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>⬇ 请在这里填写</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>一、基本信息</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>1. 游戏名称</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>游戏的完整中文名称</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>游戏的完整中文名称。</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>燕云十六州</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>2. 游戏风格 / 世界观</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>例如：古风武侠、西幻奇幻、科幻末日、现代都市……
-一两句话描述游戏背景即可</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>一两句定调，模型据此定身份。
+例如：古风武侠、西幻奇幻、科幻末日、现代都市……</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>古风武侠开放世界，五代乱世背景，含墨家机关术。</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>3. 本次任务说明</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>例如：抽取游戏内所有专有名词供翻译团队使用</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>二、要提取的内容（告诉 AI 抓什么）</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="160" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>4. 必须提取的术语类型</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>用自然语言列出所有需要提取的类型。
-例如：
-· 所有人名/NPC名（不管主次）
-· 武学招式名
-· 地点、建筑名
-· 门派、组织名
-· 道具、圣物名
-· 战斗技能/BUFF名
-……越详细越好</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>5. 不要提取的内容</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>例如：
-· 日常通用物品（木炭、草鞋）
-· 泛称/称谓（大侠、公子、弟子）
-· 时间词（子时、春分）
-· 成语固定短语</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="100" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>6. 特别注意事项</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>有没有容易搞混的边界情况？
-例如：
-· "青"单独出现时是角色名要提取，但"青色"不要
-· 带"老X、小X、阿X"前缀的一律是人名要提取
-· 排行式命名（戈老大、戈老二）全部提取</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>一句话说明用途。</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>抽取游戏内所有专有名词，供翻译团队使用。</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>二、要提取的内容（告诉 AI 抓什么 · 影响最大）</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>4. ★ 必须提取的术语类型</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>逐类列全，越详细越好。
+⚠ 关键：用「出现即提取，不论主次」这种绝对口吻，别用「重要的/酌情」——系统要 3 轮一致才保留，口径越绝对越不漏。</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>· 所有人名/NPC名（含路人、单次提及，出现即提取）
+· 武学招式 / 心法
+· 墨家机关术
+· 地名建筑、门派势力
+· 道具圣物、货币资源
+· 战斗 BUFF / 机制、UI 系统、玩法机制</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14" ht="128" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>5. ★ 不要提取的内容</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>列出噪音类型，这是降噪主力。</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>· 通用日常物品（木炭、草鞋、柴火）
+· 泛称/称谓（大侠、公子、弟子、长老）
+· 无专名场所（书房、医馆、夜市）
+· 成语（一飞冲天）
+· 时间词（子时、春分）</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>6. ★ 特别注意事项</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>专写容易搞混的边界规则，写成可判定的硬规则。</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>· 老X/小X/阿X、X嫂/X爷/X娘 一律人名，一个不漏
+· 排行命名（戈老大、戈老二、钱二娘）全部提取
+· 单字动物名作角色名时提取（青、燕、隼）
+·「青」是角色名要提，「青色」不提</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>三、术语分类</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="200" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="160" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>7. 术语分类列表</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>列出这个游戏的术语分类，每行一个。
-常见参考：
-NPC名、BOSS名、武学招式、武学心法、
-地名建筑、场景区域、门派势力、组织帮会、
-道具物品、圣物法宝、代币货币、资源材料、
-战斗BUFF、战斗机制、UI系统、玩法机制、
-任务名、成就称号、外观皮肤
-（可以直接复制修改，也可自己写）</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>每行一类，够用即可，别过细——分类太多太细模型会摇摆。
+可直接复制示例改。</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>武学招式、武学心法、墨家机关、NPC名、BOSS名、
+门派势力、地名建筑、道具物品、圣物法宝、
+代币货币、资源材料、战斗BUFF、战斗机制、
+UI系统、玩法机制、任务名</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>四、翻译策略（选填）</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>8. 目标语言</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>例如：英文、日文、韩文、繁体中文……</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>默认中→英。</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>9. 翻译策略说明</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>对各类术语的翻译方向说明。
-例如：
-· 人名：音译（拼音）
-· 招式名：意译，传达含义
-· 地点：意译为主
-· 称谓（公子、长老）：对应英文 Master / Elder
-如果没有特别要求，写"统一意译"即可</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>五、举例（越多越准确）</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="200" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>10. 应该提取的例子</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>贴几条游戏原文，标注哪些词是术语。
-格式随意，例如：
-「万大海常年往来于沦波坊和神仙渡」
-→ 万大海（NPC名）、沦波坊（地名）、神仙渡（地名）
-多写几条，覆盖不同类型的术语</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19" ht="120" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>11. 不该提取的例子</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>贴几条不含术语、或容易误判的原文。
-格式随意，例如：
-「用木炭生火，草鞋踩在石板上」→ 无术语
-「先生说弟子不得擅自出门」→ 无术语（先生/弟子是泛称）</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>各类译法方向。无特别要求写「统一意译」即可。</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>· 人名 → 音译（拼音）
+· 招式/心法 → 意译，传达含义
+· 地点 → 意译为主
+· 道具 → 简洁意译
+· 称谓 → 公子=Master，长老=Elder</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>五、举例（最影响准确率 · 正例提召回，负例提精度）</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="130" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>10. ★ 应该提取的例子</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>贴几条原文 + 标出哪些是术语、属哪类。
+覆盖各种类型，越多越准。</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>「万大海常年往来于沦波坊和神仙渡」
+→ 万大海(NPC名)、沦波坊(地名建筑)、神仙渡(地名建筑)
+「青长老说墨门弟子需恪守门规」
+→ 青长老(NPC名)、墨门(门派势力)、门规(玩法机制)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>11. ★ 不该提取的例子</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>⚠ 必填，至少 3–5 条「整句无术语」或易误判的句子。
+只给正例不给负例 → 噪音飙升。</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>「用木炭生火，草鞋踩在石板上」→ 无术语
+「长老说弟子们不得擅自出门，游侠也不例外」
+　→ 无术语（长老/弟子/游侠是泛称）
+「他一飞冲天，大鹏展翅般冲出」→ 无术语（成语）</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>六、其他补充（选填）</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="80" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="72" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>12. 其他说明</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>有什么额外需要告知的信息，都可以写在这里。</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>任何额外需要告知的信息。</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>（如：某些章节用方言；客户要求保留繁体专名……）</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
